--- a/Output Data Tables/APAT Outputs/Utilization Metrics Tables/2025/APTL_by_Aircraft_and_Airline_2025.xlsx
+++ b/Output Data Tables/APAT Outputs/Utilization Metrics Tables/2025/APTL_by_Aircraft_and_Airline_2025.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="76" uniqueCount="76">
   <si>
     <t>Row</t>
   </si>
@@ -36,6 +36,15 @@
     <t>E175</t>
   </si>
   <si>
+    <t>Q100</t>
+  </si>
+  <si>
+    <t>Q200</t>
+  </si>
+  <si>
+    <t>Q300</t>
+  </si>
+  <si>
     <t>Q400</t>
   </si>
   <si>
@@ -217,6 +226,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -265,7 +286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -292,7 +313,11 @@
     <col min="22" max="22" width="4.5703125" customWidth="true"/>
     <col min="23" max="23" width="8.85546875" customWidth="true"/>
     <col min="24" max="24" width="8.7109375" customWidth="true"/>
-    <col min="25" max="25" width="10.85546875" customWidth="true"/>
+    <col min="25" max="25" width="5.140625" customWidth="true"/>
+    <col min="26" max="26" width="7" customWidth="true"/>
+    <col min="27" max="27" width="5.5703125" customWidth="true"/>
+    <col min="28" max="28" width="8.85546875" customWidth="true"/>
+    <col min="29" max="29" width="10.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -300,76 +325,88 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="U1" s="0" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="V1" s="0" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="W1" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="X1" s="0" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Y1" s="0" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="Z1" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2">
@@ -448,6 +485,18 @@
       <c r="Y2" s="0">
         <v>0</v>
       </c>
+      <c r="Z2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -525,6 +574,18 @@
       <c r="Y3" s="0">
         <v>0</v>
       </c>
+      <c r="Z3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -600,6 +661,18 @@
         <v>0</v>
       </c>
       <c r="Y4" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>319</v>
+      </c>
+      <c r="AC4" s="0">
         <v>319</v>
       </c>
     </row>
@@ -677,6 +750,18 @@
         <v>327</v>
       </c>
       <c r="Y5" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="0">
+        <v>327</v>
+      </c>
+      <c r="AC5" s="0">
         <v>327</v>
       </c>
     </row>
@@ -754,6 +839,18 @@
         <v>0</v>
       </c>
       <c r="Y6" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="0">
+        <v>422</v>
+      </c>
+      <c r="AC6" s="0">
         <v>422</v>
       </c>
     </row>
@@ -831,6 +928,18 @@
         <v>533</v>
       </c>
       <c r="Y7" s="0">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="0">
+        <v>530</v>
+      </c>
+      <c r="AC7" s="0">
         <v>530</v>
       </c>
     </row>
@@ -910,6 +1019,18 @@
       <c r="Y8" s="0">
         <v>0</v>
       </c>
+      <c r="Z8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -964,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="0">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="S9" s="0">
         <v>0</v>
@@ -982,10 +1103,22 @@
         <v>0</v>
       </c>
       <c r="X9" s="0">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="0">
-        <v>355</v>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1035,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="0">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="0">
         <v>0</v>
@@ -1053,16 +1186,28 @@
         <v>0</v>
       </c>
       <c r="V10" s="0">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="W10" s="0">
         <v>0</v>
       </c>
       <c r="X10" s="0">
-        <v>470</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="0">
-        <v>449</v>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1082,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>640</v>
+        <v>0</v>
       </c>
       <c r="G11" s="0">
         <v>0</v>
@@ -1094,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0">
-        <v>440</v>
+        <v>0</v>
       </c>
       <c r="K11" s="0">
         <v>0</v>
@@ -1139,7 +1284,19 @@
         <v>0</v>
       </c>
       <c r="Y11" s="0">
-        <v>499</v>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1189,34 +1346,46 @@
         <v>0</v>
       </c>
       <c r="P12" s="0">
-        <v>464</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="0">
         <v>0</v>
       </c>
       <c r="R12" s="0">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="S12" s="0">
         <v>0</v>
       </c>
       <c r="T12" s="0">
-        <v>524</v>
+        <v>0</v>
       </c>
       <c r="U12" s="0">
         <v>0</v>
       </c>
       <c r="V12" s="0">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="W12" s="0">
         <v>0</v>
       </c>
       <c r="X12" s="0">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="Y12" s="0">
-        <v>456</v>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="0">
+        <v>355</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>355</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>931</v>
+        <v>0</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -1266,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="0">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="Q13" s="0">
         <v>0</v>
@@ -1284,16 +1453,28 @@
         <v>0</v>
       </c>
       <c r="V13" s="0">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="W13" s="0">
         <v>0</v>
       </c>
       <c r="X13" s="0">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="Y13" s="0">
-        <v>931</v>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="0">
+        <v>449</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>449</v>
       </c>
     </row>
     <row r="14">
@@ -1313,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>902</v>
+        <v>640</v>
       </c>
       <c r="G14" s="0">
-        <v>1116</v>
+        <v>0</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -1325,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0">
-        <v>869</v>
+        <v>440</v>
       </c>
       <c r="K14" s="0">
         <v>0</v>
@@ -1370,7 +1551,19 @@
         <v>0</v>
       </c>
       <c r="Y14" s="0">
-        <v>942</v>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="0">
+        <v>499</v>
+      </c>
+      <c r="AA14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="0">
+        <v>499</v>
       </c>
     </row>
     <row r="15">
@@ -1381,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="0">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>677</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -1393,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>818</v>
+        <v>0</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -1408,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="L15" s="0">
-        <v>1143</v>
+        <v>0</v>
       </c>
       <c r="M15" s="0">
         <v>0</v>
       </c>
       <c r="N15" s="0">
-        <v>778</v>
+        <v>0</v>
       </c>
       <c r="O15" s="0">
         <v>0</v>
       </c>
       <c r="P15" s="0">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="Q15" s="0">
         <v>0</v>
@@ -1432,22 +1625,34 @@
         <v>0</v>
       </c>
       <c r="T15" s="0">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="U15" s="0">
         <v>0</v>
       </c>
       <c r="V15" s="0">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="W15" s="0">
         <v>0</v>
       </c>
       <c r="X15" s="0">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="Y15" s="0">
-        <v>744</v>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="0">
+        <v>456</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>456</v>
       </c>
     </row>
     <row r="16">
@@ -1458,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="0">
-        <v>952</v>
+        <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>737</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -1470,28 +1675,28 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>817</v>
+        <v>931</v>
       </c>
       <c r="H16" s="0">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="I16" s="0">
         <v>0</v>
       </c>
       <c r="J16" s="0">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="K16" s="0">
         <v>0</v>
       </c>
       <c r="L16" s="0">
-        <v>906</v>
+        <v>0</v>
       </c>
       <c r="M16" s="0">
         <v>0</v>
       </c>
       <c r="N16" s="0">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="O16" s="0">
         <v>0</v>
@@ -1524,7 +1729,19 @@
         <v>0</v>
       </c>
       <c r="Y16" s="0">
-        <v>939</v>
+        <v>931</v>
+      </c>
+      <c r="Z16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>931</v>
       </c>
     </row>
     <row r="17">
@@ -1544,25 +1761,25 @@
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <v>0</v>
+        <v>902</v>
       </c>
       <c r="G17" s="0">
-        <v>0</v>
+        <v>1116</v>
       </c>
       <c r="H17" s="0">
-        <v>887</v>
+        <v>0</v>
       </c>
       <c r="I17" s="0">
         <v>0</v>
       </c>
       <c r="J17" s="0">
-        <v>0</v>
+        <v>869</v>
       </c>
       <c r="K17" s="0">
         <v>0</v>
       </c>
       <c r="L17" s="0">
-        <v>1012</v>
+        <v>0</v>
       </c>
       <c r="M17" s="0">
         <v>0</v>
@@ -1601,7 +1818,19 @@
         <v>0</v>
       </c>
       <c r="Y17" s="0">
-        <v>935</v>
+        <v>1116</v>
+      </c>
+      <c r="Z17" s="0">
+        <v>884</v>
+      </c>
+      <c r="AA17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>942</v>
       </c>
     </row>
     <row r="18">
@@ -1612,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="D18" s="0">
-        <v>1131</v>
+        <v>677</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -1624,28 +1853,28 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>1032</v>
+        <v>818</v>
       </c>
       <c r="H18" s="0">
-        <v>964</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
         <v>0</v>
       </c>
       <c r="J18" s="0">
-        <v>1935</v>
+        <v>0</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>936</v>
+        <v>1143</v>
       </c>
       <c r="M18" s="0">
         <v>0</v>
       </c>
       <c r="N18" s="0">
-        <v>0</v>
+        <v>778</v>
       </c>
       <c r="O18" s="0">
         <v>0</v>
@@ -1678,7 +1907,19 @@
         <v>0</v>
       </c>
       <c r="Y18" s="0">
-        <v>1158</v>
+        <v>733</v>
+      </c>
+      <c r="Z18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="0">
+        <v>844</v>
+      </c>
+      <c r="AB18" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="0">
+        <v>744</v>
       </c>
     </row>
     <row r="19">
@@ -1689,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="0">
-        <v>0</v>
+        <v>952</v>
       </c>
       <c r="D19" s="0">
-        <v>1679</v>
+        <v>737</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -1701,28 +1942,28 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>1893</v>
+        <v>817</v>
       </c>
       <c r="H19" s="0">
-        <v>1001</v>
+        <v>876</v>
       </c>
       <c r="I19" s="0">
-        <v>2504</v>
+        <v>0</v>
       </c>
       <c r="J19" s="0">
-        <v>2457</v>
+        <v>1140</v>
       </c>
       <c r="K19" s="0">
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>1059</v>
+        <v>906</v>
       </c>
       <c r="M19" s="0">
         <v>0</v>
       </c>
       <c r="N19" s="0">
-        <v>1229</v>
+        <v>848</v>
       </c>
       <c r="O19" s="0">
         <v>0</v>
@@ -1755,7 +1996,19 @@
         <v>0</v>
       </c>
       <c r="Y19" s="0">
-        <v>1523</v>
+        <v>804</v>
+      </c>
+      <c r="Z19" s="0">
+        <v>1140</v>
+      </c>
+      <c r="AA19" s="0">
+        <v>929</v>
+      </c>
+      <c r="AB19" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="0">
+        <v>939</v>
       </c>
     </row>
     <row r="20">
@@ -1781,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>887</v>
       </c>
       <c r="I20" s="0">
         <v>0</v>
@@ -1793,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="M20" s="0">
         <v>0</v>
@@ -1833,6 +2086,18 @@
       </c>
       <c r="Y20" s="0">
         <v>0</v>
+      </c>
+      <c r="Z20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="0">
+        <v>935</v>
+      </c>
+      <c r="AB20" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>935</v>
       </c>
     </row>
     <row r="21">
@@ -1846,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>1131</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1855,22 +2120,22 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="H21" s="0">
-        <v>0</v>
+        <v>964</v>
       </c>
       <c r="I21" s="0">
         <v>0</v>
       </c>
       <c r="J21" s="0">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="K21" s="0">
         <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="M21" s="0">
         <v>0</v>
@@ -1909,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Y21" s="0">
-        <v>0</v>
+        <v>1091</v>
+      </c>
+      <c r="Z21" s="0">
+        <v>1935</v>
+      </c>
+      <c r="AA21" s="0">
+        <v>948</v>
+      </c>
+      <c r="AB21" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="0">
+        <v>1158</v>
       </c>
     </row>
     <row r="22">
@@ -1923,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>1679</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1932,28 +2209,28 @@
         <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>422</v>
+        <v>1893</v>
       </c>
       <c r="H22" s="0">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="I22" s="0">
-        <v>140</v>
+        <v>2504</v>
       </c>
       <c r="J22" s="0">
-        <v>0</v>
+        <v>2457</v>
       </c>
       <c r="K22" s="0">
         <v>0</v>
       </c>
       <c r="L22" s="0">
-        <v>0</v>
+        <v>1059</v>
       </c>
       <c r="M22" s="0">
         <v>0</v>
       </c>
       <c r="N22" s="0">
-        <v>0</v>
+        <v>1229</v>
       </c>
       <c r="O22" s="0">
         <v>0</v>
@@ -1986,7 +2263,19 @@
         <v>0</v>
       </c>
       <c r="Y22" s="0">
-        <v>340</v>
+        <v>1656</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>2476</v>
+      </c>
+      <c r="AA22" s="0">
+        <v>1022</v>
+      </c>
+      <c r="AB22" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="0">
+        <v>1523</v>
       </c>
     </row>
     <row r="23">
@@ -2065,6 +2354,18 @@
       <c r="Y23" s="0">
         <v>0</v>
       </c>
+      <c r="Z23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
@@ -2142,6 +2443,18 @@
       <c r="Y24" s="0">
         <v>0</v>
       </c>
+      <c r="Z24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
@@ -2163,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="G25" s="0">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="H25" s="0">
         <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J25" s="0">
         <v>0</v>
@@ -2217,7 +2530,19 @@
         <v>0</v>
       </c>
       <c r="Y25" s="0">
-        <v>0</v>
+        <v>422</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>140</v>
+      </c>
+      <c r="AA25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="0">
+        <v>340</v>
       </c>
     </row>
     <row r="26">
@@ -2225,7 +2550,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
         <v>0</v>
@@ -2234,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>683</v>
+        <v>0</v>
       </c>
       <c r="F26" s="0">
         <v>0</v>
@@ -2252,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="L26" s="0">
         <v>0</v>
@@ -2261,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="0">
-        <v>893</v>
+        <v>0</v>
       </c>
       <c r="O26" s="0">
         <v>0</v>
@@ -2294,7 +2619,19 @@
         <v>0</v>
       </c>
       <c r="Y26" s="0">
-        <v>711</v>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2302,22 +2639,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>1318</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>962</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="F27" s="0">
         <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>973</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
         <v>0</v>
@@ -2329,16 +2666,16 @@
         <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>863</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
         <v>0</v>
       </c>
       <c r="M27" s="0">
-        <v>1211</v>
+        <v>0</v>
       </c>
       <c r="N27" s="0">
-        <v>981</v>
+        <v>0</v>
       </c>
       <c r="O27" s="0">
         <v>0</v>
@@ -2371,7 +2708,19 @@
         <v>0</v>
       </c>
       <c r="Y27" s="0">
-        <v>963</v>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2379,13 +2728,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>1528</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>822</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>1254</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -2406,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>924</v>
+        <v>0</v>
       </c>
       <c r="L28" s="0">
         <v>0</v>
@@ -2415,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="0">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="O28" s="0">
         <v>0</v>
@@ -2448,7 +2797,19 @@
         <v>0</v>
       </c>
       <c r="Y28" s="0">
-        <v>1083</v>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2456,7 +2817,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>875</v>
+        <v>635</v>
       </c>
       <c r="C29" s="0">
         <v>0</v>
@@ -2465,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="0">
-        <v>0</v>
+        <v>683</v>
       </c>
       <c r="F29" s="0">
         <v>0</v>
@@ -2483,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="L29" s="0">
         <v>0</v>
       </c>
       <c r="M29" s="0">
-        <v>1315</v>
+        <v>0</v>
       </c>
       <c r="N29" s="0">
-        <v>1002</v>
+        <v>893</v>
       </c>
       <c r="O29" s="0">
         <v>0</v>
@@ -2525,7 +2886,19 @@
         <v>0</v>
       </c>
       <c r="Y29" s="0">
-        <v>983</v>
+        <v>893</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>698</v>
+      </c>
+      <c r="AA29" s="0">
+        <v>683</v>
+      </c>
+      <c r="AB29" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="0">
+        <v>711</v>
       </c>
     </row>
     <row r="30">
@@ -2533,22 +2906,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>1498</v>
+        <v>1318</v>
       </c>
       <c r="C30" s="0">
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>0</v>
+        <v>962</v>
       </c>
       <c r="E30" s="0">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="F30" s="0">
         <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="H30" s="0">
         <v>0</v>
@@ -2560,16 +2933,16 @@
         <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>0</v>
+        <v>863</v>
       </c>
       <c r="L30" s="0">
         <v>0</v>
       </c>
       <c r="M30" s="0">
-        <v>0</v>
+        <v>1211</v>
       </c>
       <c r="N30" s="0">
-        <v>1132</v>
+        <v>981</v>
       </c>
       <c r="O30" s="0">
         <v>0</v>
@@ -2602,7 +2975,19 @@
         <v>0</v>
       </c>
       <c r="Y30" s="0">
-        <v>1111</v>
+        <v>968</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>932</v>
+      </c>
+      <c r="AA30" s="0">
+        <v>1152</v>
+      </c>
+      <c r="AB30" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="0">
+        <v>963</v>
       </c>
     </row>
     <row r="31">
@@ -2610,13 +2995,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>1622</v>
+        <v>1528</v>
       </c>
       <c r="C31" s="0">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="D31" s="0">
-        <v>0</v>
+        <v>1254</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
@@ -2637,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>0</v>
+        <v>924</v>
       </c>
       <c r="L31" s="0">
         <v>0</v>
@@ -2646,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="0">
-        <v>1442</v>
+        <v>1432</v>
       </c>
       <c r="O31" s="0">
         <v>0</v>
@@ -2679,7 +3064,19 @@
         <v>0</v>
       </c>
       <c r="Y31" s="0">
-        <v>1518</v>
+        <v>1359</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>936</v>
+      </c>
+      <c r="AA31" s="0">
+        <v>822</v>
+      </c>
+      <c r="AB31" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="0">
+        <v>1083</v>
       </c>
     </row>
     <row r="32">
@@ -2687,7 +3084,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="C32" s="0">
         <v>0</v>
@@ -2702,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>988</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
         <v>0</v>
@@ -2720,10 +3117,10 @@
         <v>0</v>
       </c>
       <c r="M32" s="0">
-        <v>0</v>
+        <v>1315</v>
       </c>
       <c r="N32" s="0">
-        <v>2308</v>
+        <v>1002</v>
       </c>
       <c r="O32" s="0">
         <v>0</v>
@@ -2756,7 +3153,19 @@
         <v>0</v>
       </c>
       <c r="Y32" s="0">
-        <v>1262</v>
+        <v>1002</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>875</v>
+      </c>
+      <c r="AA32" s="0">
+        <v>1315</v>
+      </c>
+      <c r="AB32" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="0">
+        <v>983</v>
       </c>
     </row>
     <row r="33">
@@ -2764,7 +3173,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0</v>
+        <v>1498</v>
       </c>
       <c r="C33" s="0">
         <v>0</v>
@@ -2779,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>1319</v>
+        <v>955</v>
       </c>
       <c r="H33" s="0">
         <v>0</v>
@@ -2800,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="0">
-        <v>1584</v>
+        <v>1132</v>
       </c>
       <c r="O33" s="0">
         <v>0</v>
@@ -2833,7 +3242,19 @@
         <v>0</v>
       </c>
       <c r="Y33" s="0">
-        <v>1441</v>
+        <v>1026</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>1498</v>
+      </c>
+      <c r="AA33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="0">
+        <v>1111</v>
       </c>
     </row>
     <row r="34">
@@ -2841,7 +3262,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0</v>
+        <v>1622</v>
       </c>
       <c r="C34" s="0">
         <v>0</v>
@@ -2856,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="0">
-        <v>2876</v>
+        <v>0</v>
       </c>
       <c r="H34" s="0">
         <v>0</v>
@@ -2877,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="0">
-        <v>3909</v>
+        <v>1442</v>
       </c>
       <c r="O34" s="0">
         <v>0</v>
@@ -2910,7 +3331,19 @@
         <v>0</v>
       </c>
       <c r="Y34" s="0">
-        <v>3220</v>
+        <v>1442</v>
+      </c>
+      <c r="Z34" s="0">
+        <v>1622</v>
+      </c>
+      <c r="AA34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="0">
+        <v>1518</v>
       </c>
     </row>
     <row r="35">
@@ -2933,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>3540</v>
+        <v>988</v>
       </c>
       <c r="H35" s="0">
         <v>0</v>
@@ -2954,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="0">
-        <v>3872</v>
+        <v>2308</v>
       </c>
       <c r="O35" s="0">
         <v>0</v>
@@ -2987,7 +3420,19 @@
         <v>0</v>
       </c>
       <c r="Y35" s="0">
-        <v>3668</v>
+        <v>1262</v>
+      </c>
+      <c r="Z35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="0">
+        <v>1262</v>
       </c>
     </row>
     <row r="36">
@@ -3010,13 +3455,13 @@
         <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>4086</v>
+        <v>1319</v>
       </c>
       <c r="H36" s="0">
         <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>3126</v>
+        <v>0</v>
       </c>
       <c r="J36" s="0">
         <v>0</v>
@@ -3031,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="0">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="O36" s="0">
         <v>0</v>
@@ -3064,7 +3509,19 @@
         <v>0</v>
       </c>
       <c r="Y36" s="0">
-        <v>3338</v>
+        <v>1441</v>
+      </c>
+      <c r="Z36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="0">
+        <v>1441</v>
       </c>
     </row>
     <row r="37">
@@ -3087,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="0">
-        <v>4088</v>
+        <v>2876</v>
       </c>
       <c r="H37" s="0">
         <v>0</v>
@@ -3108,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="N37" s="0">
-        <v>0</v>
+        <v>3909</v>
       </c>
       <c r="O37" s="0">
         <v>0</v>
@@ -3141,7 +3598,19 @@
         <v>0</v>
       </c>
       <c r="Y37" s="0">
-        <v>4088</v>
+        <v>3220</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="0">
+        <v>3220</v>
       </c>
     </row>
     <row r="38">
@@ -3164,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="0">
-        <v>4407</v>
+        <v>3540</v>
       </c>
       <c r="H38" s="0">
         <v>0</v>
@@ -3185,7 +3654,7 @@
         <v>0</v>
       </c>
       <c r="N38" s="0">
-        <v>0</v>
+        <v>3872</v>
       </c>
       <c r="O38" s="0">
         <v>0</v>
@@ -3218,7 +3687,19 @@
         <v>0</v>
       </c>
       <c r="Y38" s="0">
-        <v>4407</v>
+        <v>3668</v>
+      </c>
+      <c r="Z38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="0">
+        <v>3668</v>
       </c>
     </row>
     <row r="39">
@@ -3241,13 +3722,13 @@
         <v>0</v>
       </c>
       <c r="G39" s="0">
-        <v>5630</v>
+        <v>4086</v>
       </c>
       <c r="H39" s="0">
         <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>0</v>
+        <v>3126</v>
       </c>
       <c r="J39" s="0">
         <v>0</v>
@@ -3295,7 +3776,19 @@
         <v>0</v>
       </c>
       <c r="Y39" s="0">
-        <v>5630</v>
+        <v>4086</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>3126</v>
+      </c>
+      <c r="AA39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="0">
+        <v>3338</v>
       </c>
     </row>
     <row r="40">
@@ -3309,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="0">
-        <v>4030</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
         <v>0</v>
@@ -3318,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="0">
-        <v>0</v>
+        <v>4088</v>
       </c>
       <c r="H40" s="0">
         <v>0</v>
@@ -3339,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="0">
-        <v>4464</v>
+        <v>0</v>
       </c>
       <c r="O40" s="0">
         <v>0</v>
@@ -3372,7 +3865,19 @@
         <v>0</v>
       </c>
       <c r="Y40" s="0">
-        <v>4125</v>
+        <v>4088</v>
+      </c>
+      <c r="Z40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="0">
+        <v>4088</v>
       </c>
     </row>
     <row r="41">
@@ -3386,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="0">
-        <v>4804</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0">
         <v>0</v>
@@ -3395,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="0">
-        <v>0</v>
+        <v>4407</v>
       </c>
       <c r="H41" s="0">
         <v>0</v>
       </c>
       <c r="I41" s="0">
-        <v>3134</v>
+        <v>0</v>
       </c>
       <c r="J41" s="0">
         <v>0</v>
@@ -3416,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="N41" s="0">
-        <v>5671</v>
+        <v>0</v>
       </c>
       <c r="O41" s="0">
         <v>0</v>
@@ -3449,7 +3954,19 @@
         <v>0</v>
       </c>
       <c r="Y41" s="0">
-        <v>5175</v>
+        <v>4407</v>
+      </c>
+      <c r="Z41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="0">
+        <v>4407</v>
       </c>
     </row>
     <row r="42">
@@ -3472,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="0">
-        <v>0</v>
+        <v>5630</v>
       </c>
       <c r="H42" s="0">
         <v>0</v>
@@ -3493,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="0">
-        <v>4493</v>
+        <v>0</v>
       </c>
       <c r="O42" s="0">
         <v>0</v>
@@ -3526,7 +4043,19 @@
         <v>0</v>
       </c>
       <c r="Y42" s="0">
-        <v>4493</v>
+        <v>5630</v>
+      </c>
+      <c r="Z42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="0">
+        <v>5630</v>
       </c>
     </row>
     <row r="43">
@@ -3540,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="0">
-        <v>4194</v>
+        <v>4030</v>
       </c>
       <c r="E43" s="0">
         <v>0</v>
@@ -3570,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="N43" s="0">
-        <v>3715</v>
+        <v>4464</v>
       </c>
       <c r="O43" s="0">
         <v>0</v>
@@ -3603,7 +4132,19 @@
         <v>0</v>
       </c>
       <c r="Y43" s="0">
-        <v>3880</v>
+        <v>4125</v>
+      </c>
+      <c r="Z43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="0">
+        <v>4125</v>
       </c>
     </row>
     <row r="44">
@@ -3617,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="0">
-        <v>4410</v>
+        <v>4804</v>
       </c>
       <c r="E44" s="0">
         <v>0</v>
@@ -3632,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="0">
-        <v>0</v>
+        <v>3134</v>
       </c>
       <c r="J44" s="0">
         <v>0</v>
@@ -3647,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="N44" s="0">
-        <v>5122</v>
+        <v>5671</v>
       </c>
       <c r="O44" s="0">
         <v>0</v>
@@ -3680,7 +4221,19 @@
         <v>0</v>
       </c>
       <c r="Y44" s="0">
-        <v>4798</v>
+        <v>5328</v>
+      </c>
+      <c r="Z44" s="0">
+        <v>3134</v>
+      </c>
+      <c r="AA44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="0">
+        <v>5175</v>
       </c>
     </row>
     <row r="45">
@@ -3688,75 +4241,354 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
+        <v>0</v>
+      </c>
+      <c r="C45" s="0">
+        <v>0</v>
+      </c>
+      <c r="D45" s="0">
+        <v>0</v>
+      </c>
+      <c r="E45" s="0">
+        <v>0</v>
+      </c>
+      <c r="F45" s="0">
+        <v>0</v>
+      </c>
+      <c r="G45" s="0">
+        <v>0</v>
+      </c>
+      <c r="H45" s="0">
+        <v>0</v>
+      </c>
+      <c r="I45" s="0">
+        <v>0</v>
+      </c>
+      <c r="J45" s="0">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0">
+        <v>0</v>
+      </c>
+      <c r="L45" s="0">
+        <v>0</v>
+      </c>
+      <c r="M45" s="0">
+        <v>0</v>
+      </c>
+      <c r="N45" s="0">
+        <v>4493</v>
+      </c>
+      <c r="O45" s="0">
+        <v>0</v>
+      </c>
+      <c r="P45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="0">
+        <v>0</v>
+      </c>
+      <c r="R45" s="0">
+        <v>0</v>
+      </c>
+      <c r="S45" s="0">
+        <v>0</v>
+      </c>
+      <c r="T45" s="0">
+        <v>0</v>
+      </c>
+      <c r="U45" s="0">
+        <v>0</v>
+      </c>
+      <c r="V45" s="0">
+        <v>0</v>
+      </c>
+      <c r="W45" s="0">
+        <v>0</v>
+      </c>
+      <c r="X45" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="0">
+        <v>4493</v>
+      </c>
+      <c r="Z45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="0">
+        <v>4493</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="0">
+        <v>0</v>
+      </c>
+      <c r="C46" s="0">
+        <v>0</v>
+      </c>
+      <c r="D46" s="0">
+        <v>4194</v>
+      </c>
+      <c r="E46" s="0">
+        <v>0</v>
+      </c>
+      <c r="F46" s="0">
+        <v>0</v>
+      </c>
+      <c r="G46" s="0">
+        <v>0</v>
+      </c>
+      <c r="H46" s="0">
+        <v>0</v>
+      </c>
+      <c r="I46" s="0">
+        <v>0</v>
+      </c>
+      <c r="J46" s="0">
+        <v>0</v>
+      </c>
+      <c r="K46" s="0">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0">
+        <v>0</v>
+      </c>
+      <c r="M46" s="0">
+        <v>0</v>
+      </c>
+      <c r="N46" s="0">
+        <v>3715</v>
+      </c>
+      <c r="O46" s="0">
+        <v>0</v>
+      </c>
+      <c r="P46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="0">
+        <v>0</v>
+      </c>
+      <c r="R46" s="0">
+        <v>0</v>
+      </c>
+      <c r="S46" s="0">
+        <v>0</v>
+      </c>
+      <c r="T46" s="0">
+        <v>0</v>
+      </c>
+      <c r="U46" s="0">
+        <v>0</v>
+      </c>
+      <c r="V46" s="0">
+        <v>0</v>
+      </c>
+      <c r="W46" s="0">
+        <v>0</v>
+      </c>
+      <c r="X46" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="0">
+        <v>3880</v>
+      </c>
+      <c r="Z46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="0">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="0">
+        <v>0</v>
+      </c>
+      <c r="C47" s="0">
+        <v>0</v>
+      </c>
+      <c r="D47" s="0">
+        <v>4410</v>
+      </c>
+      <c r="E47" s="0">
+        <v>0</v>
+      </c>
+      <c r="F47" s="0">
+        <v>0</v>
+      </c>
+      <c r="G47" s="0">
+        <v>0</v>
+      </c>
+      <c r="H47" s="0">
+        <v>0</v>
+      </c>
+      <c r="I47" s="0">
+        <v>0</v>
+      </c>
+      <c r="J47" s="0">
+        <v>0</v>
+      </c>
+      <c r="K47" s="0">
+        <v>0</v>
+      </c>
+      <c r="L47" s="0">
+        <v>0</v>
+      </c>
+      <c r="M47" s="0">
+        <v>0</v>
+      </c>
+      <c r="N47" s="0">
+        <v>5122</v>
+      </c>
+      <c r="O47" s="0">
+        <v>0</v>
+      </c>
+      <c r="P47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="0">
+        <v>0</v>
+      </c>
+      <c r="R47" s="0">
+        <v>0</v>
+      </c>
+      <c r="S47" s="0">
+        <v>0</v>
+      </c>
+      <c r="T47" s="0">
+        <v>0</v>
+      </c>
+      <c r="U47" s="0">
+        <v>0</v>
+      </c>
+      <c r="V47" s="0">
+        <v>0</v>
+      </c>
+      <c r="W47" s="0">
+        <v>0</v>
+      </c>
+      <c r="X47" s="0">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="0">
+        <v>4798</v>
+      </c>
+      <c r="Z47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="0">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="0">
+        <v>4798</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="0">
         <v>1458</v>
       </c>
-      <c r="C45" s="0">
+      <c r="C48" s="0">
         <v>923</v>
       </c>
-      <c r="D45" s="0">
+      <c r="D48" s="0">
         <v>1332</v>
       </c>
-      <c r="E45" s="0">
+      <c r="E48" s="0">
         <v>842</v>
       </c>
-      <c r="F45" s="0">
+      <c r="F48" s="0">
         <v>884</v>
       </c>
-      <c r="G45" s="0">
+      <c r="G48" s="0">
         <v>1407</v>
       </c>
-      <c r="H45" s="0">
+      <c r="H48" s="0">
         <v>938</v>
       </c>
-      <c r="I45" s="0">
+      <c r="I48" s="0">
         <v>1666</v>
       </c>
-      <c r="J45" s="0">
+      <c r="J48" s="0">
         <v>1357</v>
       </c>
-      <c r="K45" s="0">
+      <c r="K48" s="0">
         <v>821</v>
       </c>
-      <c r="L45" s="0">
+      <c r="L48" s="0">
         <v>978</v>
       </c>
-      <c r="M45" s="0">
+      <c r="M48" s="0">
         <v>1212</v>
       </c>
-      <c r="N45" s="0">
+      <c r="N48" s="0">
         <v>1738</v>
       </c>
-      <c r="O45" s="0">
+      <c r="O48" s="0">
         <v>372</v>
       </c>
-      <c r="P45" s="0">
+      <c r="P48" s="0">
         <v>449</v>
       </c>
-      <c r="Q45" s="0">
+      <c r="Q48" s="0">
         <v>533</v>
       </c>
-      <c r="R45" s="0">
+      <c r="R48" s="0">
         <v>377</v>
       </c>
-      <c r="S45" s="0">
+      <c r="S48" s="0">
         <v>469</v>
       </c>
-      <c r="T45" s="0">
+      <c r="T48" s="0">
         <v>631</v>
       </c>
-      <c r="U45" s="0">
+      <c r="U48" s="0">
         <v>288</v>
       </c>
-      <c r="V45" s="0">
+      <c r="V48" s="0">
         <v>475</v>
       </c>
-      <c r="W45" s="0">
+      <c r="W48" s="0">
         <v>492</v>
       </c>
-      <c r="X45" s="0">
+      <c r="X48" s="0">
         <v>477</v>
       </c>
-      <c r="Y45" s="0">
+      <c r="Y48" s="0">
+        <v>1482</v>
+      </c>
+      <c r="Z48" s="0">
+        <v>1027</v>
+      </c>
+      <c r="AA48" s="0">
+        <v>962</v>
+      </c>
+      <c r="AB48" s="0">
+        <v>476</v>
+      </c>
+      <c r="AC48" s="0">
         <v>1167</v>
       </c>
     </row>
